--- a/saidas/metricas_resumo/valor/5_b_top_5/parte_3_recorte_de_marco.xlsx
+++ b/saidas/metricas_resumo/valor/5_b_top_5/parte_3_recorte_de_marco.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Modelo</t>
   </si>
@@ -49,40 +49,28 @@
     <t>SARIMA</t>
   </si>
   <si>
-    <t>ExtraTrees(EXT,j90)</t>
-  </si>
-  <si>
-    <t>POLY+ABR</t>
+    <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
   </si>
   <si>
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
-    <t>Voting(GBR+XGB+RFR)</t>
-  </si>
-  <si>
-    <t>8/18</t>
-  </si>
-  <si>
-    <t>11/18</t>
-  </si>
-  <si>
-    <t>9/18</t>
-  </si>
-  <si>
-    <t>7/18</t>
-  </si>
-  <si>
-    <t>13/18</t>
-  </si>
-  <si>
-    <t>14/18</t>
-  </si>
-  <si>
-    <t>12/18</t>
-  </si>
-  <si>
-    <t>18/18</t>
+    <t>10/22</t>
+  </si>
+  <si>
+    <t>7/22</t>
+  </si>
+  <si>
+    <t>17/22</t>
+  </si>
+  <si>
+    <t>16/22</t>
+  </si>
+  <si>
+    <t>15/22</t>
+  </si>
+  <si>
+    <t>22/22</t>
   </si>
 </sst>
 </file>
@@ -440,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -480,31 +468,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>6.12</v>
+        <v>5.87</v>
       </c>
       <c r="C2">
-        <v>7.48</v>
+        <v>7.05</v>
       </c>
       <c r="D2">
-        <v>0.321</v>
+        <v>0.364</v>
       </c>
       <c r="E2">
-        <v>47871.5</v>
+        <v>70161.89999999999</v>
       </c>
       <c r="F2">
-        <v>384341.4</v>
+        <v>360603.2</v>
       </c>
       <c r="G2">
-        <v>13.3</v>
+        <v>13.22</v>
       </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -512,31 +500,31 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>6.02</v>
+        <v>6.78</v>
       </c>
       <c r="C3">
-        <v>8.83</v>
+        <v>9.07</v>
       </c>
       <c r="D3">
-        <v>0.185</v>
+        <v>0.035</v>
       </c>
       <c r="E3">
-        <v>-36981.5</v>
+        <v>11190.6</v>
       </c>
       <c r="F3">
-        <v>422852.4</v>
+        <v>452579.1</v>
       </c>
       <c r="G3">
-        <v>28.29</v>
+        <v>24.93</v>
       </c>
       <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -544,95 +532,31 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>7.47</v>
+        <v>7.88</v>
       </c>
       <c r="C4">
-        <v>9.890000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D4">
-        <v>-0.043</v>
+        <v>-0.016</v>
       </c>
       <c r="E4">
-        <v>-14958.2</v>
+        <v>-52597.3</v>
       </c>
       <c r="F4">
-        <v>479715.1</v>
+        <v>461367.4</v>
       </c>
       <c r="G4">
-        <v>26.36</v>
+        <v>18.33</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>7.77</v>
-      </c>
-      <c r="C5">
-        <v>11.18</v>
-      </c>
-      <c r="D5">
-        <v>-0.269</v>
-      </c>
-      <c r="E5">
-        <v>-105978.8</v>
-      </c>
-      <c r="F5">
-        <v>518702.3</v>
-      </c>
-      <c r="G5">
-        <v>34.9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>7.68</v>
-      </c>
-      <c r="C6">
-        <v>10.09</v>
-      </c>
-      <c r="D6">
-        <v>-0.119</v>
-      </c>
-      <c r="E6">
-        <v>21410.9</v>
-      </c>
-      <c r="F6">
-        <v>496795.2</v>
-      </c>
-      <c r="G6">
-        <v>27.58</v>
-      </c>
-      <c r="H6" t="s">
         <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
